--- a/data/valores_caudalimetro/registro_caudalimetros.xlsx
+++ b/data/valores_caudalimetro/registro_caudalimetros.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bleon\Desktop\pjn\Projects\p_pozos\data\valores_caudalimetro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bleon\Desktop\ds\data\valores_caudalimetro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51849362-C3E2-45D0-B4F1-18772AF67CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A207214-D6F0-40AC-9DB6-8447A599BC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BA5E21C-C677-4CAD-86C7-F5D38D2B73F6}"/>
   </bookViews>
@@ -496,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -510,7 +510,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
